--- a/ex02/ex02.xlsx
+++ b/ex02/ex02.xlsx
@@ -1,88 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anano\Desktop\Excel\Phase_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f2ee41b75427174/Desktop/excel/ex02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0F35F3-0BA0-4733-96ED-38FB96DFE62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9C0F35F3-0BA0-4733-96ED-38FB96DFE62C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD5EEC5A-40C1-4153-BE97-1A1BEAA1DF52}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Dept Code</t>
   </si>
   <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>E101</t>
-  </si>
-  <si>
-    <t>Isla</t>
-  </si>
-  <si>
     <t>HR</t>
   </si>
   <si>
-    <t>E102</t>
-  </si>
-  <si>
-    <t>Jon</t>
-  </si>
-  <si>
     <t>FN</t>
   </si>
   <si>
-    <t>E103</t>
-  </si>
-  <si>
-    <t>Karen</t>
-  </si>
-  <si>
     <t>IT</t>
   </si>
   <si>
-    <t>E104</t>
-  </si>
-  <si>
-    <t>Liam</t>
-  </si>
-  <si>
     <t>MK</t>
   </si>
   <si>
-    <t>E105</t>
-  </si>
-  <si>
-    <t>Mina</t>
-  </si>
-  <si>
     <t>SL</t>
   </si>
   <si>
@@ -120,13 +87,61 @@
   </si>
   <si>
     <t>Band 4</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Attendance %</t>
+  </si>
+  <si>
+    <t>Amira</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Chloe</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Farid</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>Pass/Fail</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Bonus credit</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Score scale</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,13 +168,44 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -168,21 +214,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -200,27 +231,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,98 +557,282 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="13.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="16.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2">
-        <v>61000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2">
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2">
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="2">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="6">
+        <v>92</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.96</v>
+      </c>
+      <c r="D2" s="8" t="str">
+        <f>IF(B2 &gt; 60, "Pass", "Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="E2" s="9" t="str">
+        <f>_xlfn.IFS(B2&gt;90, "A", B2&gt;80, "B", B2&gt;70, "C", B2&gt;60, "D", TRUE,  "F")</f>
+        <v>A</v>
+      </c>
+      <c r="F2" s="9" t="str">
+        <f>_xlfn.IFS(AND(B2 &gt;= 80, C2 &gt;= 90%), "Eligible", TRUE,  "Noneligible")</f>
+        <v>Eligible</v>
+      </c>
+      <c r="G2" s="9" t="str">
+        <f>_xlfn.IFS(OR(B2&lt;60,C2&lt;80%),"Needs Review", TRUE,"OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="H2" s="9" t="str">
+        <f>_xlfn.IFS(AND(B2&gt;90, C2&gt;95%), "Excellent", TRUE, "Standard")</f>
+        <v>Excellent</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="6">
+        <v>77</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="D3" s="8" t="str">
+        <f t="shared" ref="D3:D9" si="0">IF(B3 &gt; 60, "Pass", "Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="E3" s="9" t="str">
+        <f t="shared" ref="E3:E9" si="1">_xlfn.IFS(B3&gt;90, "A", B3&gt;80, "B", B3&gt;70, "C", B3&gt;60, "D", TRUE,  "F")</f>
+        <v>C</v>
+      </c>
+      <c r="F3" s="9" t="str">
+        <f t="shared" ref="F3:F9" si="2">_xlfn.IFS(AND(B3 &gt;= 80, C3 &gt;= 90%), "Eligible", TRUE,  "Noneligible")</f>
+        <v>Noneligible</v>
+      </c>
+      <c r="G3" s="9" t="str">
+        <f t="shared" ref="G3:G9" si="3">_xlfn.IFS(OR(B3&lt;60,C3&lt;80%),"Needs Review", TRUE,"OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="H3" s="9" t="str">
+        <f t="shared" ref="H3:H9" si="4">_xlfn.IFS(AND(B3&gt;90, C3&gt;95%), "Excellent", TRUE, "Standard")</f>
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6">
+        <v>64</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="D4" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E4" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>D</v>
+      </c>
+      <c r="F4" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Noneligible</v>
+      </c>
+      <c r="G4" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
+      <c r="H4" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="6">
+        <v>58</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="D5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E5" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>F</v>
+      </c>
+      <c r="F5" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Noneligible</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Needs Review</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6">
+        <v>85</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.98</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E6" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
+      <c r="F6" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Eligible</v>
+      </c>
+      <c r="G6" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
+      <c r="H6" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="6">
+        <v>73</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.79</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E7" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>C</v>
+      </c>
+      <c r="F7" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Noneligible</v>
+      </c>
+      <c r="G7" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Needs Review</v>
+      </c>
+      <c r="H7" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6">
+        <v>49</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E8" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>F</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Noneligible</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>Needs Review</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6">
+        <v>68</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E9" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>D</v>
+      </c>
+      <c r="F9" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Noneligible</v>
+      </c>
+      <c r="G9" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>OK</v>
+      </c>
+      <c r="H9" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>Standard</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -603,54 +843,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147240CF-1136-4E24-8ECC-F1B01A765340}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="23.21875" defaultRowHeight="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>24</v>
+    </row>
+    <row r="5" spans="1:2" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -661,49 +901,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AF20C3-DC28-4D25-A213-8CB5E6BE33DB}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
+    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>55000</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>65000</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>70000</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
